--- a/gridcraft/gc_sort_collation.xlsx
+++ b/gridcraft/gc_sort_collation.xlsx
@@ -424,11 +424,11 @@
         </is>
       </c>
       <c r="C1">
-        <f>SORT(A1:A19)</f>
+        <f>_xlfn._xlws.SORT(A1:A19)</f>
         <v/>
       </c>
       <c r="E1">
-        <f>SORTBY(A1:A19,A1:A19,-1)</f>
+        <f>_xlfn.SORTBY(A1:A19,A1:A19,-1)</f>
         <v/>
       </c>
       <c r="G1" t="inlineStr">

--- a/gridcraft/gc_sort_collation.xlsx
+++ b/gridcraft/gc_sort_collation.xlsx
@@ -12,6 +12,28 @@
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,13 +445,11 @@
           <t>x-1</t>
         </is>
       </c>
-      <c r="C1">
-        <f>_xlfn._xlws.SORT(A1:A19)</f>
-        <v/>
-      </c>
-      <c r="E1">
-        <f>_xlfn.SORTBY(A1:A19,A1:A19,-1)</f>
-        <v/>
+      <c r="C1" cm="1">
+        <f t="array" ref="C1:C19">_xlfn._xlws.SORT(A1:A19)</f>
+      </c>
+      <c r="E1" cm="1">
+        <f t="array" ref="E1:E19">_xlfn.SORTBY(A1:A19,A1:A19,-1)</f>
       </c>
       <c r="G1" t="inlineStr">
         <is>
